--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484073_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484073_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8621</v>
+        <v>5.8978</v>
       </c>
       <c r="E2" t="n">
-        <v>2.345</v>
+        <v>2.5491</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5171</v>
+        <v>3.3487</v>
       </c>
       <c r="G2" t="n">
         <v>2.4472</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0181</v>
+        <v>0.0538</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8105</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8286</v>
+        <v>0.6602</v>
       </c>
       <c r="V2" t="n">
         <v>1.8097</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8782</v>
+        <v>4.3757</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2969</v>
+        <v>1.9908</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5813</v>
+        <v>2.3849</v>
       </c>
       <c r="G3" t="n">
         <v>3.0083</v>
@@ -688,13 +688,13 @@
         <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6796</v>
+        <v>0.1771</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2438</v>
+        <v>-0.0623</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4358</v>
+        <v>0.2394</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1649</v>
+        <v>2.2738</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6954</v>
+        <v>2.7092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4695</v>
+        <v>-0.4354</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2895</v>
+        <v>1.509</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2222</v>
+        <v>-0.9629</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0673</v>
+        <v>2.4719</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1516</v>
+        <v>3.2715</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1089</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0427</v>
+        <v>2.5754</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4411</v>
+        <v>-1.7625</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3311</v>
+        <v>-1.659</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.11</v>
+        <v>-0.1035</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3968</v>
+        <v>-1.5871</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4544</v>
+        <v>-0.632</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6746</v>
+        <v>-0.4477</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7798</v>
+        <v>-0.1843</v>
       </c>
       <c r="V4" t="n">
         <v>0.6032</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>1.4724</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3373</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1566</v>
+        <v>1.1542</v>
       </c>
       <c r="E5" t="n">
-        <v>2.097</v>
+        <v>0.4974</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9404</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>1.509</v>
+        <v>0.4911</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9629</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4719</v>
+        <v>-0.0376</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2715</v>
+        <v>2.0617</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6961000000000001</v>
+        <v>1.4516</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5754</v>
+        <v>0.6101</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7625</v>
+        <v>-1.5707</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.659</v>
+        <v>-0.923</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1035</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.5871</v>
+        <v>-1.3887</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7492</v>
+        <v>0.068</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0599</v>
+        <v>-0.1757</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6893</v>
+        <v>0.2436</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.901</v>
+        <v>1.1497</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4449</v>
+        <v>1.1853</v>
       </c>
       <c r="F6" t="n">
-        <v>0.456</v>
+        <v>-0.0355</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2272</v>
+        <v>-0.2895</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1208</v>
+        <v>-0.2222</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1064</v>
+        <v>-0.0673</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7486</v>
+        <v>1.1516</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3831</v>
+        <v>1.1089</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3655</v>
+        <v>0.0427</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5214</v>
+        <v>-1.4411</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2623</v>
+        <v>-1.3311</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2591</v>
+        <v>-0.11</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3894</v>
+        <v>0.4393</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3117</v>
+        <v>0.1644</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.2748</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.532</v>
+        <v>0.6032</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.532</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8478</v>
+        <v>0.929</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7634</v>
+        <v>0.4449</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6112</v>
+        <v>0.4841</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2011</v>
+        <v>1.2272</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0635</v>
+        <v>0.1208</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1376</v>
+        <v>1.1064</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1079</v>
+        <v>1.7486</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2553</v>
+        <v>0.3831</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8525</v>
+        <v>1.3655</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.5214</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1918</v>
+        <v>-0.2623</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2851</v>
+        <v>-0.2591</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.3725</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0278</v>
+        <v>-0.3614</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4988</v>
+        <v>-0.3117</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4709</v>
+        <v>-0.0496</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1352</v>
+        <v>-0.532</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1352</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8297</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5575</v>
+        <v>-0.7634</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7278</v>
+        <v>1.5271</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5592</v>
+        <v>3.2011</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2677</v>
+        <v>1.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2916</v>
+        <v>2.1376</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3315</v>
+        <v>3.1079</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5283</v>
+        <v>1.2553</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8032</v>
+        <v>1.8525</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7723</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2606</v>
+        <v>-0.1918</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5117</v>
+        <v>0.2851</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.5871</v>
+        <v>-3.3725</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3498</v>
+        <v>-0.112</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4876</v>
+        <v>-0.4988</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1378</v>
+        <v>0.3868</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.881</v>
+        <v>-1.1352</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7563</v>
+        <v>0.47</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0128</v>
+        <v>1.9453</v>
       </c>
       <c r="F9" t="n">
-        <v>0.769</v>
+        <v>-1.4753</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4911</v>
+        <v>2.5592</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5286999999999999</v>
+        <v>2.2677</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0376</v>
+        <v>0.2916</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0617</v>
+        <v>4.3315</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4516</v>
+        <v>3.5283</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6101</v>
+        <v>0.8032</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5707</v>
+        <v>-1.7723</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.923</v>
+        <v>-1.2606</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.5117</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3887</v>
+        <v>-1.5871</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3299</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6858</v>
+        <v>-0.1246</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3559</v>
+        <v>0.1147</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.881</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6753</v>
+        <v>-2.5631</v>
       </c>
       <c r="E12" t="n">
         <v>-2.8761</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2008</v>
+        <v>0.313</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4432</v>
@@ -1390,13 +1390,13 @@
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4466</v>
+        <v>-0.3344</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6474</v>
+        <v>-3.3771</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2343</v>
+        <v>-4.1323</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5869</v>
+        <v>0.7552</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1693</v>
@@ -1468,13 +1468,13 @@
         <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0975</v>
+        <v>0.1728</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.255</v>
+        <v>-0.153</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1575</v>
+        <v>0.3258</v>
       </c>
       <c r="V13" t="n">
         <v>0.6032</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.6707</v>
+        <v>10.6704</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5501</v>
+        <v>3.5502</v>
       </c>
       <c r="F14" t="n">
-        <v>7.120399999999999</v>
+        <v>7.1204</v>
       </c>
       <c r="G14" t="n">
         <v>11.1379</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0732</v>
+        <v>3.073199999999999</v>
       </c>
       <c r="I14" t="n">
         <v>8.0649</v>
@@ -1537,7 +1537,7 @@
         <v>-1.1329</v>
       </c>
       <c r="P14" t="n">
-        <v>9.99999999995449e-05</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.8546</v>
@@ -1546,10 +1546,10 @@
         <v>17.8545</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5385000000000002</v>
+        <v>-0.5387</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.4651</v>
+        <v>-2.4652</v>
       </c>
       <c r="U14" t="n">
         <v>1.9264</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.553000000000001</v>
+        <v>7.9714</v>
       </c>
       <c r="E15" t="n">
-        <v>6.6567</v>
+        <v>5.7384</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8963</v>
+        <v>2.233</v>
       </c>
       <c r="G15" t="n">
         <v>4.547</v>
@@ -1624,13 +1624,13 @@
         <v>2.7774</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9217</v>
+        <v>0.3401</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9297</v>
+        <v>0.0115</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.008</v>
+        <v>0.3287</v>
       </c>
       <c r="V15" t="n">
         <v>1.4971</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3059</v>
+        <v>2.0713</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.367</v>
+        <v>-0.2649</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6729</v>
+        <v>2.3362</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8793</v>
@@ -1702,13 +1702,13 @@
         <v>2.9758</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6087</v>
+        <v>0.3741</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.493</v>
+        <v>-0.391</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1018</v>
+        <v>0.7651</v>
       </c>
       <c r="V16" t="n">
         <v>2.7749</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2189</v>
+        <v>-0.9766</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0744</v>
+        <v>-1.9724</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8555</v>
+        <v>0.9958</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6233</v>
@@ -1780,13 +1780,13 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1559</v>
+        <v>0.0864</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2494</v>
+        <v>-0.1474</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0935</v>
+        <v>0.2338</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2413</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4396</v>
+        <v>-1.233</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6128</v>
+        <v>-1.7148</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1732</v>
+        <v>0.4818</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4555</v>
@@ -1858,13 +1858,13 @@
         <v>2.7774</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.3131</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.493</v>
+        <v>-0.595</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0267</v>
+        <v>0.2819</v>
       </c>
       <c r="V18" t="n">
         <v>-0.266</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>J. MIRANDA VARGAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5619</v>
+        <v>-2.4665</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0051</v>
+        <v>-0.8871</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5568</v>
+        <v>-1.5794</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3913</v>
+        <v>-2.2084</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8315</v>
+        <v>-1.6125</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5598</v>
+        <v>-0.5959</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.257</v>
+        <v>1.3063</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2971</v>
+        <v>0.0562</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>1.2501</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1343</v>
+        <v>-3.5148</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5344</v>
+        <v>-1.6687</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6</v>
+        <v>-1.846</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0278</v>
+        <v>-0.1374</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2438</v>
+        <v>-0.2096</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.216</v>
+        <v>0.0722</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.1206</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MIRANDA VARGAS</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1527</v>
+        <v>-2.5797</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6013</v>
+        <v>-1.1071</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5513</v>
+        <v>-1.4726</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2084</v>
+        <v>-2.3913</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6125</v>
+        <v>-0.8315</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5959</v>
+        <v>-1.5598</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3063</v>
+        <v>-0.257</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0562</v>
+        <v>-0.2971</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2501</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.5148</v>
+        <v>-2.1343</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6687</v>
+        <v>-0.5344</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.846</v>
+        <v>-1.6</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8236</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9238</v>
+        <v>0.1417</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1002</v>
+        <v>-0.1318</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6639</v>
+        <v>-3.6818</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2323</v>
+        <v>-2.3344</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4316</v>
+        <v>-1.3474</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9545</v>
@@ -2092,13 +2092,13 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2885</v>
+        <v>0.2707</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0567</v>
+        <v>-0.0453</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2318</v>
+        <v>0.316</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5931</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3647</v>
+        <v>-4.8012</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9427</v>
+        <v>-0.8394</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4221</v>
+        <v>-3.9618</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8619</v>
+        <v>-2.3105</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.517</v>
+        <v>-0.4034</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3449</v>
+        <v>-1.9071</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1216</v>
+        <v>1.5582</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7566000000000001</v>
+        <v>1.0686</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6349</v>
+        <v>0.4896</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.9836</v>
+        <v>-3.8687</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.2736</v>
+        <v>-1.472</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.71</v>
+        <v>-2.3967</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9758</v>
+        <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3806</v>
+        <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7668</v>
+        <v>-0.2493</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.68</v>
+        <v>-0.2153</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4469</v>
+        <v>-0.034</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6745</v>
+        <v>-1.4478</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.266</v>
+        <v>-1.4478</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1276</v>
+        <v>-4.9743</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9414</v>
+        <v>-3.7386</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.1863</v>
+        <v>-1.2357</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3105</v>
+        <v>-3.8619</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4034</v>
+        <v>-1.517</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9071</v>
+        <v>-2.3449</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5582</v>
+        <v>0.1216</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0686</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4896</v>
+        <v>-0.6349</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.8687</v>
+        <v>-3.9836</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.472</v>
+        <v>-2.2736</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.3967</v>
+        <v>-1.71</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1822</v>
+        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3887</v>
+        <v>2.3806</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5758</v>
+        <v>0.1573</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3173</v>
+        <v>-0.476</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2585</v>
+        <v>0.6333</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4478</v>
+        <v>-0.6745</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4478</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="24">
@@ -2287,7 +2287,7 @@
         <v>-7.120299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5502</v>
+        <v>-3.5501</v>
       </c>
       <c r="G24" t="n">
         <v>-11.1377</v>
@@ -2299,10 +2299,10 @@
         <v>-8.0648</v>
       </c>
       <c r="J24" t="n">
-        <v>8.722899999999999</v>
+        <v>8.722900000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>7.5903</v>
+        <v>7.590299999999999</v>
       </c>
       <c r="L24" t="n">
         <v>1.1329</v>
@@ -2326,16 +2326,16 @@
         <v>17.8546</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5384999999999999</v>
+        <v>0.5387</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9263</v>
+        <v>-1.9264</v>
       </c>
       <c r="U24" t="n">
-        <v>2.465</v>
+        <v>2.4652</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.07129999999999947</v>
+        <v>-0.07129999999999936</v>
       </c>
       <c r="W24" t="n">
         <v>3.9376</v>
